--- a/output/hasil_evaluasi.xlsx
+++ b/output/hasil_evaluasi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tugas Akhir\Code\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B70759A6-A3F8-4F54-B730-023A00A7E0A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DA739E-513C-4CD1-B01D-116CA683CE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A638E4B9-6C2D-4244-B379-509AEE2E0D63}"/>
   </bookViews>
@@ -958,6 +958,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0A229F7-FDEC-458A-BC69-2C934D6E6834}">
   <dimension ref="A1:H109"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="54.6328125" customWidth="1"/>
+    <col min="2" max="2" width="36.36328125" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" customWidth="1"/>
+    <col min="4" max="4" width="20.36328125" customWidth="1"/>
+    <col min="5" max="5" width="19.36328125" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="8" max="8" width="18.7265625" customWidth="1"/>
+    <col min="9" max="9" width="21.36328125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
